--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="loc_hierarchy_list" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">loc_hierarchy_list!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">loc_hierarchy_list!$C$1:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>hierarchy_level</t>
   </si>
@@ -62,34 +62,19 @@
     <t>del_dtimes</t>
   </si>
   <si>
-    <t>देश</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>System</t>
+    <t>department</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>NULL</t>
   </si>
   <si>
-    <t>राज्य</t>
-  </si>
-  <si>
-    <t>शहर</t>
-  </si>
-  <si>
-    <t>डाक कोड</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>city</t>
+    <t>province</t>
   </si>
   <si>
     <t>country</t>
@@ -101,31 +86,16 @@
     <t>es</t>
   </si>
   <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Pays</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>État</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>CódigoPostal</t>
-  </si>
-  <si>
-    <t>CodePostal</t>
-  </si>
-  <si>
-    <t>postalCode</t>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>Comuna</t>
+  </si>
+  <si>
+    <t>Commune</t>
   </si>
 </sst>
 </file>
@@ -1281,8 +1251,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9.81481481481481" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="33.2685185185185" customWidth="1"/>
+    <col min="3" max="3" width="26.8148148148148" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
@@ -1318,7 +1292,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1333,7 +1307,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1350,7 +1324,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1365,7 +1339,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1382,7 +1356,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -1397,7 +1371,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1414,13 +1388,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -1429,7 +1403,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1449,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -1461,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1484,7 +1458,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -1493,7 +1467,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1510,13 +1484,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -1525,7 +1499,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -1542,13 +1516,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -1557,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="1">
-        <v>45526.6050115472</v>
+        <v>45667.2624366394</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1572,263 +1546,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1">
-        <v>45526.6050115472</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C9" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
